--- a/china-mobile/数据源/中国移动_核心业务运营与结构转型.xlsx
+++ b/china-mobile/数据源/中国移动_核心业务运营与结构转型.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t/>
   </si>
@@ -86,11 +86,6 @@
   <si>
     <r>
       <t>算力服务收入（亿元）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>—(2025新口径)</t>
     </r>
   </si>
   <si>
@@ -887,7 +882,7 @@
   <cellStyleXfs>
     <xf numFmtId="301" fontId="8" fillId="4" borderId="2" xfId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -915,7 +910,7 @@
     <xf numFmtId="301" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="301" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -927,16 +922,13 @@
     <xf numFmtId="300" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="301" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="301" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="301" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="62" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="301" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1236,7 +1228,7 @@
   <dimension ref="H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" style="17" customWidth="1"/>
+    <col min="1" max="1" width="22.6914" style="17" customWidth="1"/>
     <col min="2" max="2" width="13" style="17" customWidth="1"/>
     <col min="3" max="3" width="13" style="17" customWidth="1"/>
     <col min="4" max="4" width="13" style="17" customWidth="1"/>
@@ -1312,17 +1304,17 @@
       <c r="A6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" s="8">
         <v>808</v>
@@ -1331,24 +1323,24 @@
         <v>898</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="9">
         <v>862</v>
@@ -1357,24 +1349,24 @@
         <v>908</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" s="12">
         <v>18.8</v>
@@ -1383,12 +1375,12 @@
         <v>20.2</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="12">
         <v>9.42</v>
@@ -1409,14 +1401,14 @@
         <v>10.05</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="18">
+        <v>23</v>
+      </c>
+      <c r="B10" s="12">
         <v>1.65</v>
       </c>
       <c r="C10" s="13">
@@ -1435,12 +1427,12 @@
         <v>6.42</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="12">
         <v>2.1</v>
@@ -1461,12 +1453,12 @@
         <v>3.29</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="12">
         <v>47.4</v>
@@ -1487,12 +1479,12 @@
         <v>47</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="12">
         <v>37.7</v>
@@ -1513,12 +1505,12 @@
         <v>44.5</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="12">
         <v>9.4</v>
@@ -1539,14 +1531,14 @@
         <v>17.3</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="18">
+        <v>33</v>
+      </c>
+      <c r="B15" s="12">
         <v>8.73</v>
       </c>
       <c r="C15" s="13">
@@ -1565,7 +1557,7 @@
         <v>14.82</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1591,399 +1583,399 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="15" t="s">
         <v>50</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="15" t="s">
         <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="15" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="15" t="s">
         <v>61</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="15" t="s">
         <v>64</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="15" t="s">
         <v>68</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="15" t="s">
         <v>72</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="15" t="s">
         <v>76</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="C14" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="15" t="s">
         <v>80</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="15" t="s">
         <v>84</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="C16" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="15" t="s">
         <v>88</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="15" t="s">
         <v>92</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="15" t="s">
         <v>96</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="D19" s="15" t="s">
         <v>100</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="C20" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="15" t="s">
         <v>104</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="C21" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="C22" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="15" t="s">
         <v>113</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="C23" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="15" t="s">
         <v>117</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="15" t="s">
         <v>120</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="C25" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="D25" s="15" t="s">
         <v>124</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="C26" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="15" t="s">
         <v>128</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="C27" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="15" t="s">
         <v>132</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="15" t="s">
         <v>138</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="15" t="s">
         <v>142</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2005,37 +1997,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="16" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="15" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="16" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="15" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="16" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="15" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="16" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="15" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="16" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="15" t="s">
+    <row r="8" spans="1:1">
+      <c r="A8" s="16" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="15" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
